--- a/接口测试用例/GreaterWMS_ASN入库链路.xlsx
+++ b/接口测试用例/GreaterWMS_ASN入库链路.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\auto-test\接口测试用例\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\test02\auto-test\接口测试用例\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56AC0676-DBDA-4ECA-BC2D-CE771BD0817C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C36BA4-F3A3-4814-B07F-079750AA39D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3670" yWindow="0" windowWidth="20800" windowHeight="14220" firstSheet="11" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="510" windowWidth="20800" windowHeight="14220" firstSheet="11" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="登录接口" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="200">
   <si>
     <t>接口Key</t>
   </si>
@@ -858,6 +858,34 @@
   </si>
   <si>
     <t>asnMoveToBin_003</t>
+  </si>
+  <si>
+    <t>login_004</t>
+  </si>
+  <si>
+    <t>登录接口-登录失败-用户名不存在</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库不存在账号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>P1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{   "name": not_exist_user
+        "password": '123456'}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>响应状态码：200
+响应格式：JSON
+code 等于 "1012"
+msg 匹配 "User Name Or Password Error"
+响应体不得返回 openid / token
+data.password 为 null 或缺失</t>
   </si>
 </sst>
 </file>
@@ -1378,9 +1406,39 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="84" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>
